--- a/artfynd/A 50877-2025 artfynd.xlsx
+++ b/artfynd/A 50877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165870</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165738</v>
       </c>
       <c r="B3" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165869</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50877-2025 artfynd.xlsx
+++ b/artfynd/A 50877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165870</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165738</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165869</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50877-2025 artfynd.xlsx
+++ b/artfynd/A 50877-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129165738</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50877-2025 artfynd.xlsx
+++ b/artfynd/A 50877-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165870</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165738</v>
       </c>
       <c r="B3" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129165869</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
